--- a/artfynd/A 15140-2026 artfynd.xlsx
+++ b/artfynd/A 15140-2026 artfynd.xlsx
@@ -675,65 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132897546</v>
+        <v>132897539</v>
       </c>
       <c r="B2" t="n">
-        <v>99132</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Antonsberget, Brännäset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531604</v>
+        <v>531599</v>
       </c>
       <c r="R2" t="n">
-        <v>7117565</v>
+        <v>7117521</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -768,11 +755,6 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Minst 100 plantor inom ca 2 m2 yta. Mattbildande.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -786,6 +768,21 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132897543</v>
+        <v>132897540</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,29 +811,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -846,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531701</v>
+        <v>531607</v>
       </c>
       <c r="R3" t="n">
-        <v>7117485</v>
+        <v>7117526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,17 +880,13 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på en gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -913,14 +905,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,32 +925,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132897538</v>
+        <v>132897550</v>
       </c>
       <c r="B4" t="n">
-        <v>83316</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -976,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>531608</v>
+        <v>531587</v>
       </c>
       <c r="R4" t="n">
-        <v>7117498</v>
+        <v>7117572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1027,6 +1014,11 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1059,14 +1051,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132897553</v>
+        <v>132897551</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1089,11 +1081,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1101,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>531682</v>
+        <v>531669</v>
       </c>
       <c r="R5" t="n">
-        <v>7117497</v>
+        <v>7117537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1189,10 +1177,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132897549</v>
+        <v>132897552</v>
       </c>
       <c r="B6" t="n">
-        <v>99132</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,54 +1188,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Antonsberget, Brännäset, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>531671</v>
+        <v>531571</v>
       </c>
       <c r="R6" t="n">
-        <v>7117492</v>
+        <v>7117516</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1282,11 +1253,6 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 20 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1300,6 +1266,26 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1317,14 +1303,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132897552</v>
+        <v>132897553</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1347,7 +1333,11 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1355,10 +1345,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>531571</v>
+        <v>531682</v>
       </c>
       <c r="R7" t="n">
-        <v>7117516</v>
+        <v>7117497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1443,10 +1433,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132897551</v>
+        <v>132897538</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>83358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,21 +1444,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1481,10 +1471,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>531669</v>
+        <v>531608</v>
       </c>
       <c r="R8" t="n">
-        <v>7117537</v>
+        <v>7117498</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1532,11 +1522,6 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1569,10 +1554,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132897542</v>
+        <v>132897545</v>
       </c>
       <c r="B9" t="n">
-        <v>57958</v>
+        <v>80488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1580,31 +1565,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1612,10 +1592,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>531580</v>
+        <v>531614</v>
       </c>
       <c r="R9" t="n">
-        <v>7117521</v>
+        <v>7117492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1650,38 +1630,19 @@
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1699,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132897540</v>
+        <v>132897541</v>
       </c>
       <c r="B10" t="n">
-        <v>91920</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,28 +1671,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1741,10 +1703,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>531607</v>
+        <v>531547</v>
       </c>
       <c r="R10" t="n">
-        <v>7117526</v>
+        <v>7117568</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1779,13 +1741,17 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1824,10 +1790,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132897550</v>
+        <v>132897542</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1835,26 +1801,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1862,10 +1833,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>531587</v>
+        <v>531580</v>
       </c>
       <c r="R11" t="n">
-        <v>7117572</v>
+        <v>7117521</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1900,24 +1871,23 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1950,10 +1920,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132897541</v>
+        <v>132897543</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1953,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1993,10 +1963,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>531547</v>
+        <v>531701</v>
       </c>
       <c r="R12" t="n">
-        <v>7117568</v>
+        <v>7117485</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2033,7 +2003,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2060,9 +2030,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2080,10 +2055,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132897545</v>
+        <v>132897544</v>
       </c>
       <c r="B13" t="n">
-        <v>80439</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2091,26 +2066,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2118,10 +2098,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>531614</v>
+        <v>531711</v>
       </c>
       <c r="R13" t="n">
-        <v>7117492</v>
+        <v>7117490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2156,19 +2136,38 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2186,52 +2185,65 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132897539</v>
+        <v>132897546</v>
       </c>
       <c r="B14" t="n">
-        <v>91920</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Antonsberget, Brännäset, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>531599</v>
+        <v>531604</v>
       </c>
       <c r="R14" t="n">
-        <v>7117521</v>
+        <v>7117565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2266,6 +2278,11 @@
           <t>2026-04-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 100 plantor inom ca 2 m2 yta. Mattbildande.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2279,21 +2296,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2314,7 +2316,7 @@
         <v>132897548</v>
       </c>
       <c r="B15" t="n">
-        <v>99132</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2439,53 +2441,65 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132897544</v>
+        <v>132897549</v>
       </c>
       <c r="B16" t="n">
-        <v>57958</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Antonsberget, Brännäset, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>531711</v>
+        <v>531671</v>
       </c>
       <c r="R16" t="n">
-        <v>7117490</v>
+        <v>7117492</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2522,7 +2536,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på en gran.</t>
+          <t>Minst 20 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2531,27 +2545,13 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>

--- a/artfynd/A 15140-2026 artfynd.xlsx
+++ b/artfynd/A 15140-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897539</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897540</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,6 +1063,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897550</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1174,6 +1194,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897551</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1300,6 +1325,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897552</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1430,6 +1460,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897553</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1551,6 +1586,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897538</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1657,6 +1697,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897545</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1787,6 +1832,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897541</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1917,6 +1967,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897542</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2052,6 +2107,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897543</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2182,6 +2242,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897544</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2310,6 +2375,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897546</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2438,6 +2508,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897548</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2566,8 +2641,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132897549</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>